--- a/Assets/Document/Poker.xlsx
+++ b/Assets/Document/Poker.xlsx
@@ -83,16 +83,64 @@
     <t>选择一名玩家发动，该玩家这局游戏发动技能有35%概率失败，可叠加</t>
   </si>
   <si>
+    <t>颠倒</t>
+  </si>
+  <si>
+    <t>选择一名玩家发动，该玩家这局游戏画面颠倒</t>
+  </si>
+  <si>
+    <t>枷锁</t>
+  </si>
+  <si>
+    <t>选择一名玩家发动，该玩家这局游戏只能再使用3次技能</t>
+  </si>
+  <si>
+    <t>共鸣</t>
+  </si>
+  <si>
+    <t>如果场上其他玩家有和你同类的牌型，这些牌会进行闪烁</t>
+  </si>
+  <si>
+    <t>援助</t>
+  </si>
+  <si>
+    <t>选择一名玩家发动，恢复其3点能量</t>
+  </si>
+  <si>
+    <t>封印</t>
+  </si>
+  <si>
+    <t>选择场上玩家一张底牌发动，这张牌被遮挡，且免疫[透视]、[变牌]、[交换]</t>
+  </si>
+  <si>
+    <t>灵机</t>
+  </si>
+  <si>
+    <t>发动后这局游戏该技能会随机变成其他任意技能</t>
+  </si>
+  <si>
+    <t>透支</t>
+  </si>
+  <si>
+    <t>能量恢复至最大，但接下来三局无法使用任何技能</t>
+  </si>
+  <si>
+    <t>交换</t>
+  </si>
+  <si>
+    <t>选择场上任意2张牌发动，将这2张牌进行调换</t>
+  </si>
+  <si>
     <t>许愿</t>
   </si>
   <si>
     <t>发动后下一局游戏的2张底牌必定是JQKA</t>
   </si>
   <si>
-    <t>交换</t>
-  </si>
-  <si>
-    <t>选择场上任意2张牌发动，将这2张牌进行调换</t>
+    <t>重力场</t>
+  </si>
+  <si>
+    <t>这局游戏场上能量最高的玩家所有技能能量消耗+2</t>
   </si>
   <si>
     <t>反射壁</t>
@@ -107,54 +155,6 @@
     <t>选择一名玩家发动，该玩家这局游戏无法弃牌</t>
   </si>
   <si>
-    <t>援助</t>
-  </si>
-  <si>
-    <t>选择一名玩家发动，恢复其3点能量</t>
-  </si>
-  <si>
-    <t>封印</t>
-  </si>
-  <si>
-    <t>选择场上玩家一张底牌发动，这张牌被遮挡，且免疫透视、变牌、交换技能</t>
-  </si>
-  <si>
-    <t>透支</t>
-  </si>
-  <si>
-    <t>能量恢复至最大，但接下来三局无法使用任何技能</t>
-  </si>
-  <si>
-    <t>共鸣</t>
-  </si>
-  <si>
-    <t>如果场上其他玩家有和你同类的牌型，这些牌会进行闪烁</t>
-  </si>
-  <si>
-    <t>灵机</t>
-  </si>
-  <si>
-    <t>发动后这局游戏该技能会随机变成其他任意技能</t>
-  </si>
-  <si>
-    <t>戏法空间</t>
-  </si>
-  <si>
-    <t>选择一名玩家发动，该玩家这局游戏画面颠倒</t>
-  </si>
-  <si>
-    <t>重力场</t>
-  </si>
-  <si>
-    <t>这局游戏场上能量最高的玩家所有技能能量消耗+2</t>
-  </si>
-  <si>
-    <t>枷锁</t>
-  </si>
-  <si>
-    <t>选择一名玩家发动，该玩家这局游戏只能再使用3次技能</t>
-  </si>
-  <si>
     <t>道具名称</t>
   </si>
   <si>
@@ -185,10 +185,10 @@
     <t>所有技能发动时间-70%</t>
   </si>
   <si>
-    <t>电池</t>
-  </si>
-  <si>
-    <t>能量上限-6，能量恢复-2，每当其他玩家使用技能，恢复1点能量</t>
+    <t>磁线圈</t>
+  </si>
+  <si>
+    <t>能量上限-6，能量恢复-2，每当其他玩家成功发动技能，恢复1点能量</t>
   </si>
   <si>
     <t>兽爪</t>
@@ -203,6 +203,18 @@
     <t>[抵抗]能量消耗-1</t>
   </si>
   <si>
+    <t>天线</t>
+  </si>
+  <si>
+    <t>[感应]不消耗能量且显示玩家饰品</t>
+  </si>
+  <si>
+    <t>帽子</t>
+  </si>
+  <si>
+    <t>发动技能时不会被[感应]效果感知</t>
+  </si>
+  <si>
     <t>镜片</t>
   </si>
   <si>
@@ -215,28 +227,16 @@
     <t>[透视]显示时间提升至60秒</t>
   </si>
   <si>
+    <t>戒指</t>
+  </si>
+  <si>
+    <t>[变牌]和[交换]可以对公牌使用</t>
+  </si>
+  <si>
     <t>音叉</t>
   </si>
   <si>
     <t>[干扰]的技能效果+25%</t>
-  </si>
-  <si>
-    <t>戒指</t>
-  </si>
-  <si>
-    <t>[变牌]和[交换]可以对公牌使用</t>
-  </si>
-  <si>
-    <t>天线</t>
-  </si>
-  <si>
-    <t>[感应]不消耗能量且显示玩家饰品</t>
-  </si>
-  <si>
-    <t>帽子</t>
-  </si>
-  <si>
-    <t>使用技能时不会被[感应]效果感知</t>
   </si>
   <si>
     <t>神像</t>
@@ -455,24 +455,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -791,7 +779,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -815,16 +803,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -833,89 +821,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -928,28 +916,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1271,8 +1240,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="4" width="10.875" style="1" customWidth="1"/>
@@ -1402,16 +1371,16 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1">
-        <v>4</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="C8" s="4">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1419,16 +1388,16 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="4">
-        <v>5</v>
-      </c>
-      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1436,16 +1405,16 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D10" s="4">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1457,10 +1426,10 @@
         <v>24</v>
       </c>
       <c r="C11" s="4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D11" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
@@ -1470,16 +1439,16 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1487,14 +1456,14 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="5">
-        <v>3</v>
-      </c>
-      <c r="D13" s="5">
-        <v>4</v>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>29</v>
@@ -1504,7 +1473,7 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="4">
@@ -1513,7 +1482,7 @@
       <c r="D14" s="4">
         <v>3</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1521,16 +1490,16 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4">
-        <v>3</v>
-      </c>
-      <c r="E15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1538,71 +1507,71 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="4">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="5">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5">
-        <v>2</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="C17" s="4">
+        <v>5</v>
+      </c>
+      <c r="D17" s="4">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="4">
+        <v>7</v>
+      </c>
+      <c r="D18" s="4">
         <v>5</v>
       </c>
-      <c r="D18" s="10">
-        <v>4</v>
-      </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="10">
-        <v>3</v>
-      </c>
-      <c r="D19" s="10">
-        <v>3</v>
-      </c>
-      <c r="E19" s="12" t="s">
+      <c r="C19" s="4">
+        <v>9</v>
+      </c>
+      <c r="D19" s="4">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
         <v>0</v>
       </c>
@@ -1613,124 +1582,126 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>2</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>3</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>4</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>5</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>6</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>8</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>9</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>10</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>11</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="6" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1741,7 +1712,7 @@
       <c r="B33" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1752,7 +1723,7 @@
       <c r="B34" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="5" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1763,7 +1734,7 @@
       <c r="B35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1774,7 +1745,7 @@
       <c r="B36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1785,7 +1756,7 @@
       <c r="B37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1854,7 +1825,7 @@
         <v>81</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1862,7 +1833,7 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>80</v>
@@ -1879,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>84</v>
@@ -1896,7 +1867,7 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>84</v>

--- a/Assets/Document/Poker.xlsx
+++ b/Assets/Document/Poker.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="147">
   <si>
     <t>No</t>
   </si>
@@ -44,6 +45,9 @@
     <t>技能效果</t>
   </si>
   <si>
+    <t>价格</t>
+  </si>
+  <si>
     <t>抵抗</t>
   </si>
   <si>
@@ -257,6 +261,27 @@
     <t>当玩家为场上亏损最高时，所有技能能量消耗-2（最低为1）</t>
   </si>
   <si>
+    <t>筹码</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>折扣后</t>
+  </si>
+  <si>
+    <t>美元</t>
+  </si>
+  <si>
+    <t>Pack</t>
+  </si>
+  <si>
+    <t>全部技能+饰品+1200钻石</t>
+  </si>
+  <si>
+    <t>永久每日钻石奖励200</t>
+  </si>
+  <si>
     <t>技能</t>
   </si>
   <si>
@@ -282,6 +307,168 @@
   </si>
   <si>
     <t>保守</t>
+  </si>
+  <si>
+    <t>标题</t>
+  </si>
+  <si>
+    <t>成就</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>久经沙场1</t>
+  </si>
+  <si>
+    <t>进行1场牌局</t>
+  </si>
+  <si>
+    <t>久经沙场2</t>
+  </si>
+  <si>
+    <t>进行10场牌局</t>
+  </si>
+  <si>
+    <t>久经沙场3</t>
+  </si>
+  <si>
+    <t>进行30场牌局</t>
+  </si>
+  <si>
+    <t>久经沙场4</t>
+  </si>
+  <si>
+    <t>进行100场牌局</t>
+  </si>
+  <si>
+    <t>久经沙场5</t>
+  </si>
+  <si>
+    <t>进行300场牌局</t>
+  </si>
+  <si>
+    <t>久经沙场6</t>
+  </si>
+  <si>
+    <t>进行500场牌局</t>
+  </si>
+  <si>
+    <t>超能大师1</t>
+  </si>
+  <si>
+    <t>使用1次技能</t>
+  </si>
+  <si>
+    <t>超能大师2</t>
+  </si>
+  <si>
+    <t>使用10次技能</t>
+  </si>
+  <si>
+    <t>超能大师3</t>
+  </si>
+  <si>
+    <t>使用30次技能</t>
+  </si>
+  <si>
+    <t>超能大师4</t>
+  </si>
+  <si>
+    <t>使用100次技能</t>
+  </si>
+  <si>
+    <t>超能大师5</t>
+  </si>
+  <si>
+    <t>使用300次技能</t>
+  </si>
+  <si>
+    <t>超能大师6</t>
+  </si>
+  <si>
+    <t>使用500次技能</t>
+  </si>
+  <si>
+    <t>攀登高峰1</t>
+  </si>
+  <si>
+    <t>累计赢得100筹码</t>
+  </si>
+  <si>
+    <t>攀登高峰2</t>
+  </si>
+  <si>
+    <t>累计赢得500筹码</t>
+  </si>
+  <si>
+    <t>攀登高峰3</t>
+  </si>
+  <si>
+    <t>累计赢得2000筹码</t>
+  </si>
+  <si>
+    <t>攀登高峰4</t>
+  </si>
+  <si>
+    <t>累计赢得5000筹码</t>
+  </si>
+  <si>
+    <t>攀登高峰5</t>
+  </si>
+  <si>
+    <t>累计赢得10000筹码</t>
+  </si>
+  <si>
+    <t>攀登高峰6</t>
+  </si>
+  <si>
+    <t>累计赢得30000筹码</t>
+  </si>
+  <si>
+    <t>一击必杀1</t>
+  </si>
+  <si>
+    <t>以”两对“牌型赢得一场牌局</t>
+  </si>
+  <si>
+    <t>一击必杀2</t>
+  </si>
+  <si>
+    <t>以”三条“牌型赢得一场牌局</t>
+  </si>
+  <si>
+    <t>一击必杀3</t>
+  </si>
+  <si>
+    <t>以”顺子“牌型赢得一场牌局</t>
+  </si>
+  <si>
+    <t>一击必杀4</t>
+  </si>
+  <si>
+    <t>以”葫芦“牌型赢得一场牌局</t>
+  </si>
+  <si>
+    <t>一击必杀5</t>
+  </si>
+  <si>
+    <t>以”同花“牌型赢得一场牌局</t>
+  </si>
+  <si>
+    <t>一击必杀6</t>
+  </si>
+  <si>
+    <t>以”四条“牌型赢得一场牌局</t>
+  </si>
+  <si>
+    <t>一击必杀7</t>
+  </si>
+  <si>
+    <t>以”同花顺“牌型赢得一场牌局</t>
+  </si>
+  <si>
+    <t>合计</t>
   </si>
 </sst>
 </file>
@@ -903,8 +1090,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1240,647 +1439,1623 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:M69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="4" width="10.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="83.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="10.875" style="5" customWidth="1"/>
+    <col min="3" max="4" width="5.16666666666667" style="5" customWidth="1"/>
+    <col min="5" max="5" width="55.95" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1">
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="D2" s="1">
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1">
+      <c r="B8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D8" s="8">
+        <v>2</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="C3" s="1">
+      <c r="B9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="8">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>3</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="8">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D10" s="8">
+        <v>3</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="8">
+        <v>3</v>
+      </c>
+      <c r="D12" s="8">
+        <v>4</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>2</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <v>3</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="8">
+        <v>4</v>
+      </c>
+      <c r="D15" s="8">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="8">
+        <v>5</v>
+      </c>
+      <c r="D17" s="8">
+        <v>4</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="8">
+        <v>7</v>
+      </c>
+      <c r="D18" s="8">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="8">
+        <v>9</v>
+      </c>
+      <c r="D19" s="8">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="J20">
+        <v>6</v>
+      </c>
+      <c r="K20">
+        <v>8</v>
+      </c>
+      <c r="L20">
+        <v>10</v>
+      </c>
+      <c r="M20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="5">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="5">
+        <v>2</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>30</v>
+      </c>
+      <c r="J23">
+        <f>I23*$J$20</f>
+        <v>180</v>
+      </c>
+      <c r="K23">
+        <f>I23*$K$20</f>
+        <v>240</v>
+      </c>
+      <c r="L23">
+        <f>I23*$L$20</f>
+        <v>300</v>
+      </c>
+      <c r="M23">
+        <f>I23*$M$20</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="5">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>20</v>
+      </c>
+      <c r="J24">
+        <f>I24*$J$20</f>
+        <v>120</v>
+      </c>
+      <c r="K24">
+        <f>I24*$K$20</f>
+        <v>160</v>
+      </c>
+      <c r="L24">
+        <f>I24*$L$20</f>
+        <v>200</v>
+      </c>
+      <c r="M24">
+        <f>I24*$M$20</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="5">
+        <v>4</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>15</v>
+      </c>
+      <c r="J25">
+        <f>I25*$J$20</f>
+        <v>90</v>
+      </c>
+      <c r="K25">
+        <f>I25*$K$20</f>
+        <v>120</v>
+      </c>
+      <c r="L25">
+        <f>I25*$L$20</f>
+        <v>150</v>
+      </c>
+      <c r="M25">
+        <f>I25*$M$20</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="5">
+        <v>5</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="1">
+        <v>400</v>
+      </c>
+      <c r="H26">
+        <v>4</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <f>I26*$J$20</f>
+        <v>60</v>
+      </c>
+      <c r="K26">
+        <f>I26*$K$20</f>
+        <v>80</v>
+      </c>
+      <c r="L26">
+        <f>I26*$L$20</f>
+        <v>100</v>
+      </c>
+      <c r="M26">
+        <f>I26*$M$20</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="5">
+        <v>6</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="1">
+        <v>400</v>
+      </c>
+      <c r="H27">
+        <v>5</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27">
+        <f>I27*$J$20</f>
+        <v>30</v>
+      </c>
+      <c r="K27">
+        <f>I27*$K$20</f>
+        <v>40</v>
+      </c>
+      <c r="L27">
+        <f>I27*$L$20</f>
+        <v>50</v>
+      </c>
+      <c r="M27">
+        <f>I27*$M$20</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="5">
+        <v>7</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" s="1">
+        <v>400</v>
+      </c>
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <f>I28*$J$20</f>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f>I28*$K$20</f>
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <f>I28*$L$20</f>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f>I28*$M$20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="5">
+        <v>8</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="1">
+        <v>400</v>
+      </c>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1">
+      <c r="B30" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="5">
+        <v>10</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="5">
+        <v>11</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5">
+        <v>12</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5">
+        <v>13</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5">
+        <v>14</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5">
+        <v>15</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="5">
+        <v>16</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="5">
+        <v>1</v>
+      </c>
+      <c r="B40" s="5">
+        <v>3000</v>
+      </c>
+      <c r="C40" s="5">
+        <v>30</v>
+      </c>
+      <c r="D40" s="5">
+        <v>30</v>
+      </c>
+      <c r="E40" s="5">
+        <f>D40/C40</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="5">
+        <v>2</v>
+      </c>
+      <c r="B41" s="5">
+        <v>6000</v>
+      </c>
+      <c r="C41" s="5">
+        <v>60</v>
+      </c>
+      <c r="D41" s="5">
+        <v>55</v>
+      </c>
+      <c r="E41" s="5">
+        <f>D41/C41</f>
+        <v>0.916666666666667</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B42" s="5">
+        <v>10000</v>
+      </c>
+      <c r="C42" s="5">
+        <v>100</v>
+      </c>
+      <c r="D42" s="5">
+        <v>90</v>
+      </c>
+      <c r="E42" s="5">
+        <f>D42/C42</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="5">
+        <v>4</v>
+      </c>
+      <c r="B43" s="5">
+        <v>30000</v>
+      </c>
+      <c r="C43" s="5">
+        <v>300</v>
+      </c>
+      <c r="D43" s="5">
+        <v>260</v>
+      </c>
+      <c r="E43" s="5">
+        <f>D43/C43</f>
+        <v>0.866666666666667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="5">
+        <v>5</v>
+      </c>
+      <c r="B44" s="5">
+        <v>50000</v>
+      </c>
+      <c r="C44" s="5">
+        <v>500</v>
+      </c>
+      <c r="D44" s="5">
+        <v>420</v>
+      </c>
+      <c r="E44" s="5">
+        <f>D44/C44</f>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="5">
+        <v>6</v>
+      </c>
+      <c r="B45" s="5">
+        <v>100000</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1000</v>
+      </c>
+      <c r="D45" s="5">
+        <v>800</v>
+      </c>
+      <c r="E45" s="5">
+        <f>D45/C45</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="5">
+        <v>7</v>
+      </c>
+      <c r="B46" s="5">
+        <v>300000</v>
+      </c>
+      <c r="C46" s="5">
+        <v>3000</v>
+      </c>
+      <c r="D46" s="5">
+        <v>2300</v>
+      </c>
+      <c r="E46" s="5">
+        <f>D46/C46</f>
+        <v>0.766666666666667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="5">
+        <v>8</v>
+      </c>
+      <c r="B47" s="5">
+        <v>500000</v>
+      </c>
+      <c r="C47" s="5">
+        <v>5000</v>
+      </c>
+      <c r="D47" s="5">
+        <v>3600</v>
+      </c>
+      <c r="E47" s="5">
+        <f>D47/C47</f>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="6"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="5">
+        <v>1</v>
+      </c>
+      <c r="B50" s="5">
+        <v>300</v>
+      </c>
+      <c r="C50" s="5">
+        <v>1</v>
+      </c>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5">
+        <f>B50/C50</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="5">
+        <v>2</v>
+      </c>
+      <c r="B51" s="5">
+        <v>630</v>
+      </c>
+      <c r="C51" s="5">
+        <v>2</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5">
+        <f>B51/C51</f>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="5">
+        <v>3</v>
+      </c>
+      <c r="B52" s="5">
+        <v>1650</v>
+      </c>
+      <c r="C52" s="5">
+        <v>5</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5">
+        <f>B52/C52</f>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="5">
+        <v>4</v>
+      </c>
+      <c r="B53" s="5">
+        <v>3500</v>
+      </c>
+      <c r="C53" s="5">
         <v>10</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D53" s="5"/>
+      <c r="E53" s="5">
+        <f>B53/C53</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="5">
+        <v>5</v>
+      </c>
+      <c r="B54" s="5">
+        <v>5600</v>
+      </c>
+      <c r="C54" s="5">
+        <v>15</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5">
+        <f>B54/C54</f>
+        <v>373.333333333333</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="5">
+        <v>6</v>
+      </c>
+      <c r="B55" s="5">
+        <v>8000</v>
+      </c>
+      <c r="C55" s="5">
+        <v>20</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5">
+        <f>B55/C55</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="5">
+        <v>7</v>
+      </c>
+      <c r="B56" s="5">
+        <v>12600</v>
+      </c>
+      <c r="C56" s="5">
+        <v>30</v>
+      </c>
+      <c r="E56" s="5">
+        <f>B56/C56</f>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="5">
+        <v>8</v>
+      </c>
+      <c r="B57" s="5">
+        <v>22000</v>
+      </c>
+      <c r="C57" s="5">
+        <v>50</v>
+      </c>
+      <c r="E57" s="5">
+        <f>B57/C57</f>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="5">
+        <v>1</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="5">
+        <v>4.99</v>
+      </c>
+      <c r="H60">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="5">
+        <v>2</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="5">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="5">
+        <v>1</v>
+      </c>
+      <c r="B64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E64" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E65" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5">
         <v>3</v>
       </c>
-      <c r="D4" s="1">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1">
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E66" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1">
-        <v>4</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1">
+      <c r="B67" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E67" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1">
+      <c r="B68" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="4">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <v>3</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="4">
-        <v>3</v>
-      </c>
-      <c r="D12" s="4">
-        <v>4</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>2</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>3</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="4">
-        <v>4</v>
-      </c>
-      <c r="D15" s="4">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="1">
-        <v>4</v>
-      </c>
-      <c r="D16" s="1">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="4">
-        <v>5</v>
-      </c>
-      <c r="D17" s="4">
-        <v>4</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="4">
-        <v>7</v>
-      </c>
-      <c r="D18" s="4">
-        <v>5</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="B69" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="4">
-        <v>9</v>
-      </c>
-      <c r="D19" s="4">
-        <v>7</v>
-      </c>
-      <c r="E19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="1">
-        <v>1</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="1">
-        <v>2</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="1">
-        <v>3</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1">
-        <v>4</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="1">
-        <v>5</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="1">
-        <v>6</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="1">
-        <v>7</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="6" t="s">
+      <c r="C69" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E69" t="s">
         <v>57</v>
-      </c>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="1">
-        <v>8</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="1">
-        <v>9</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="1">
-        <v>10</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="1">
-        <v>11</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="1">
-        <v>12</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="1">
-        <v>13</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="1">
-        <v>14</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="1">
-        <v>15</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="1">
-        <v>16</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="1">
-        <v>1</v>
-      </c>
-      <c r="B41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E41" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="1">
-        <v>2</v>
-      </c>
-      <c r="B42" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E42" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="1">
-        <v>3</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="1">
-        <v>4</v>
-      </c>
-      <c r="B44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E44" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="1">
-        <v>5</v>
-      </c>
-      <c r="B45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E45" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="1">
-        <v>6</v>
-      </c>
-      <c r="B46" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E46" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6083333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="C1"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="D28" s="1">
+        <f>SUM(D3:D27)</f>
+        <v>4500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Assets/Document/Poker.xlsx
+++ b/Assets/Document/Poker.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17775"/>
+    <workbookView windowWidth="24210" windowHeight="14955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
     <t>X</t>
   </si>
   <si>
-    <t>其他玩家向你发动技能时进行提示，技能发动完成之前可以消耗相同的能量使其发动失败</t>
+    <t>其他玩家向你发动技能时进行提示，发动完成之前消耗同等能量使其发动失败</t>
   </si>
   <si>
     <t>感应</t>
@@ -1090,7 +1090,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1101,23 +1101,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1442,44 +1430,44 @@
   <dimension ref="A1:M69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="10.875" style="5" customWidth="1"/>
-    <col min="3" max="4" width="5.16666666666667" style="5" customWidth="1"/>
-    <col min="5" max="5" width="55.95" style="5" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="9.475" style="1" customWidth="1"/>
+    <col min="5" max="5" width="65.8583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" t="s">
@@ -1490,16 +1478,16 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="5">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" t="s">
@@ -1510,16 +1498,16 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="1">
         <v>3</v>
       </c>
       <c r="E4" t="s">
@@ -1530,16 +1518,16 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="1">
         <v>4</v>
       </c>
       <c r="E5" t="s">
@@ -1550,16 +1538,16 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="5">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" t="s">
@@ -1570,19 +1558,19 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="1">
@@ -1590,19 +1578,19 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="5">
         <v>2</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="5">
         <v>2</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="6" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="1">
@@ -1610,19 +1598,19 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="5">
         <v>3</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="5">
         <v>3</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="1">
@@ -1630,19 +1618,19 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="5">
         <v>1</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="5">
         <v>3</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="1">
@@ -1650,16 +1638,16 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="5">
         <v>2</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="5">
         <v>2</v>
       </c>
       <c r="E11" t="s">
@@ -1670,19 +1658,19 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="5">
         <v>3</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="5">
         <v>4</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="1">
@@ -1690,19 +1678,19 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="5">
         <v>0</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="1">
@@ -1710,19 +1698,19 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="5">
         <v>0</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="5">
         <v>3</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F14" s="1">
@@ -1730,16 +1718,16 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="5">
         <v>4</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="5">
         <v>5</v>
       </c>
       <c r="E15" t="s">
@@ -1750,16 +1738,16 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="1">
         <v>4</v>
       </c>
       <c r="E16" t="s">
@@ -1770,19 +1758,19 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="5">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="5">
         <v>5</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="5">
         <v>4</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F17" s="1">
@@ -1790,16 +1778,16 @@
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="5">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="5">
         <v>7</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="5">
         <v>5</v>
       </c>
       <c r="E18" t="s">
@@ -1810,16 +1798,16 @@
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="5">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="5">
         <v>9</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="5">
         <v>7</v>
       </c>
       <c r="E19" t="s">
@@ -1844,24 +1832,24 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="5">
+      <c r="A22" s="1">
         <v>1</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F22" s="1">
@@ -1869,13 +1857,13 @@
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="5">
+      <c r="A23" s="1">
         <v>2</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F23" s="1">
@@ -1888,30 +1876,30 @@
         <v>30</v>
       </c>
       <c r="J23">
-        <f>I23*$J$20</f>
+        <f t="shared" ref="J23:J28" si="0">I23*$J$20</f>
         <v>180</v>
       </c>
       <c r="K23">
-        <f>I23*$K$20</f>
+        <f t="shared" ref="K23:K28" si="1">I23*$K$20</f>
         <v>240</v>
       </c>
       <c r="L23">
-        <f>I23*$L$20</f>
+        <f t="shared" ref="L23:L28" si="2">I23*$L$20</f>
         <v>300</v>
       </c>
       <c r="M23">
-        <f>I23*$M$20</f>
+        <f t="shared" ref="M23:M28" si="3">I23*$M$20</f>
         <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="5">
+      <c r="A24" s="1">
         <v>3</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F24" s="1">
@@ -1924,30 +1912,30 @@
         <v>20</v>
       </c>
       <c r="J24">
-        <f>I24*$J$20</f>
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
       <c r="K24">
-        <f>I24*$K$20</f>
+        <f t="shared" si="1"/>
         <v>160</v>
       </c>
       <c r="L24">
-        <f>I24*$L$20</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="M24">
-        <f>I24*$M$20</f>
+        <f t="shared" si="3"/>
         <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="5">
+      <c r="A25" s="1">
         <v>4</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F25" s="1">
@@ -1960,30 +1948,30 @@
         <v>15</v>
       </c>
       <c r="J25">
-        <f>I25*$J$20</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="K25">
-        <f>I25*$K$20</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="L25">
-        <f>I25*$L$20</f>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="M25">
-        <f>I25*$M$20</f>
+        <f t="shared" si="3"/>
         <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="5">
+      <c r="A26" s="1">
         <v>5</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F26" s="1">
@@ -1996,30 +1984,30 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <f>I26*$J$20</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="K26">
-        <f>I26*$K$20</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="L26">
-        <f>I26*$L$20</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="M26">
-        <f>I26*$M$20</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="5">
+      <c r="A27" s="1">
         <v>6</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="6" t="s">
         <v>56</v>
       </c>
       <c r="F27" s="1">
@@ -2032,30 +2020,30 @@
         <v>5</v>
       </c>
       <c r="J27">
-        <f>I27*$J$20</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="K27">
-        <f>I27*$K$20</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="L27">
-        <f>I27*$L$20</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="M27">
-        <f>I27*$M$20</f>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="5">
+      <c r="A28" s="1">
         <v>7</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F28" s="1">
@@ -2068,45 +2056,45 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <f>I28*$J$20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K28">
-        <f>I28*$K$20</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L28">
-        <f>I28*$L$20</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M28">
-        <f>I28*$M$20</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="5">
+      <c r="A29" s="1">
         <v>8</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F29" s="1">
         <v>400</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="1"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="5">
+      <c r="A30" s="1">
         <v>9</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="2" t="s">
         <v>62</v>
       </c>
       <c r="F30" s="1">
@@ -2114,13 +2102,13 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="5">
+      <c r="A31" s="1">
         <v>10</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="2" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="1">
@@ -2128,13 +2116,13 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="5">
+      <c r="A32" s="1">
         <v>11</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F32" s="1">
@@ -2142,13 +2130,13 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="5">
+      <c r="A33" s="1">
         <v>12</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="2" t="s">
         <v>68</v>
       </c>
       <c r="F33" s="1">
@@ -2156,13 +2144,13 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="5">
+      <c r="A34" s="1">
         <v>13</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="6" t="s">
         <v>70</v>
       </c>
       <c r="F34" s="1">
@@ -2170,13 +2158,13 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="5">
+      <c r="A35" s="1">
         <v>14</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F35" s="1">
@@ -2184,13 +2172,13 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="5">
+      <c r="A36" s="1">
         <v>15</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F36" s="1">
@@ -2198,13 +2186,13 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="5">
+      <c r="A37" s="1">
         <v>16</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F37" s="1">
@@ -2212,317 +2200,311 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="5">
+      <c r="A40" s="1">
         <v>1</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="1">
         <v>3000</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="1">
         <v>30</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="1">
         <v>30</v>
       </c>
-      <c r="E40" s="5">
-        <f>D40/C40</f>
+      <c r="E40" s="1">
+        <f t="shared" ref="E40:E47" si="4">D40/C40</f>
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="5">
+      <c r="A41" s="1">
         <v>2</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="1">
         <v>6000</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="1">
         <v>60</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="1">
         <v>55</v>
       </c>
-      <c r="E41" s="5">
-        <f>D41/C41</f>
+      <c r="E41" s="1">
+        <f t="shared" si="4"/>
         <v>0.916666666666667</v>
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="5">
+      <c r="A42" s="1">
         <v>3</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="1">
         <v>10000</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="1">
         <v>100</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="1">
         <v>90</v>
       </c>
-      <c r="E42" s="5">
-        <f>D42/C42</f>
+      <c r="E42" s="1">
+        <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="5">
+      <c r="A43" s="1">
         <v>4</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="1">
         <v>30000</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="1">
         <v>300</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="1">
         <v>260</v>
       </c>
-      <c r="E43" s="5">
-        <f>D43/C43</f>
+      <c r="E43" s="1">
+        <f t="shared" si="4"/>
         <v>0.866666666666667</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="5">
+      <c r="A44" s="1">
         <v>5</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="1">
         <v>50000</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="1">
         <v>500</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="1">
         <v>420</v>
       </c>
-      <c r="E44" s="5">
-        <f>D44/C44</f>
+      <c r="E44" s="1">
+        <f t="shared" si="4"/>
         <v>0.84</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="5">
+      <c r="A45" s="1">
         <v>6</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="1">
         <v>100000</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="1">
         <v>1000</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="1">
         <v>800</v>
       </c>
-      <c r="E45" s="5">
-        <f>D45/C45</f>
+      <c r="E45" s="1">
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="5">
+      <c r="A46" s="1">
         <v>7</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="1">
         <v>300000</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="1">
         <v>3000</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="1">
         <v>2300</v>
       </c>
-      <c r="E46" s="5">
-        <f>D46/C46</f>
+      <c r="E46" s="1">
+        <f t="shared" si="4"/>
         <v>0.766666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="5">
+      <c r="A47" s="1">
         <v>8</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="1">
         <v>500000</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="1">
         <v>5000</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="1">
         <v>3600</v>
       </c>
-      <c r="E47" s="5">
-        <f>D47/C47</f>
+      <c r="E47" s="1">
+        <f t="shared" si="4"/>
         <v>0.72</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="6"/>
+      <c r="D49" s="3"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="5">
+      <c r="A50" s="1">
         <v>1</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="1">
         <v>300</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="1">
         <v>1</v>
       </c>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5">
-        <f>B50/C50</f>
+      <c r="E50" s="1">
+        <f t="shared" ref="E50:E57" si="5">B50/C50</f>
         <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="5">
+      <c r="A51" s="1">
         <v>2</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="1">
         <v>630</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="1">
         <v>2</v>
       </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5">
-        <f>B51/C51</f>
+      <c r="E51" s="1">
+        <f t="shared" si="5"/>
         <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="5">
+      <c r="A52" s="1">
         <v>3</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="1">
         <v>1650</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="1">
         <v>5</v>
       </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5">
-        <f>B52/C52</f>
+      <c r="E52" s="1">
+        <f t="shared" si="5"/>
         <v>330</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="5">
+      <c r="A53" s="1">
         <v>4</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="1">
         <v>3500</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53" s="1">
         <v>10</v>
       </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5">
-        <f>B53/C53</f>
+      <c r="E53" s="1">
+        <f t="shared" si="5"/>
         <v>350</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="5">
+      <c r="A54" s="1">
         <v>5</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="1">
         <v>5600</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54" s="1">
         <v>15</v>
       </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5">
-        <f>B54/C54</f>
+      <c r="E54" s="1">
+        <f t="shared" si="5"/>
         <v>373.333333333333</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="5">
+      <c r="A55" s="1">
         <v>6</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="1">
         <v>8000</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="1">
         <v>20</v>
       </c>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5">
-        <f>B55/C55</f>
+      <c r="E55" s="1">
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="5">
+      <c r="A56" s="1">
         <v>7</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="1">
         <v>12600</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="1">
         <v>30</v>
       </c>
-      <c r="E56" s="5">
-        <f>B56/C56</f>
+      <c r="E56" s="1">
+        <f t="shared" si="5"/>
         <v>420</v>
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="5">
+      <c r="A57" s="1">
         <v>8</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="1">
         <v>22000</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="1">
         <v>50</v>
       </c>
-      <c r="E57" s="5">
-        <f>B57/C57</f>
+      <c r="E57" s="1">
+        <f t="shared" si="5"/>
         <v>440</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="5">
+      <c r="A60" s="1">
         <v>1</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="1">
         <v>4.99</v>
       </c>
       <c r="H60">
@@ -2530,44 +2512,44 @@
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="5">
+      <c r="A61" s="1">
         <v>2</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="1">
         <v>1.99</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="5">
+      <c r="A64" s="1">
         <v>1</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E64" t="s">
@@ -2575,16 +2557,16 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="5">
+      <c r="A65" s="1">
         <v>2</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E65" t="s">
@@ -2592,16 +2574,16 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="5">
+      <c r="A66" s="1">
         <v>3</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E66" t="s">
@@ -2609,16 +2591,16 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="5">
+      <c r="A67" s="1">
         <v>4</v>
       </c>
       <c r="B67" t="s">
         <v>35</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D67" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E67" t="s">
@@ -2626,16 +2608,16 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="5">
+      <c r="A68" s="1">
         <v>5</v>
       </c>
       <c r="B68" t="s">
         <v>35</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E68" t="s">
@@ -2643,16 +2625,16 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="5">
+      <c r="A69" s="1">
         <v>6</v>
       </c>
       <c r="B69" t="s">
         <v>39</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E69" t="s">
@@ -2701,7 +2683,7 @@
       <c r="B3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D3" s="1">
@@ -2715,7 +2697,7 @@
       <c r="B4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D4" s="1">
@@ -2729,7 +2711,7 @@
       <c r="B5" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D5" s="1">
@@ -2743,7 +2725,7 @@
       <c r="B6" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D6" s="1">
@@ -2757,7 +2739,7 @@
       <c r="B7" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D7" s="1">
@@ -2771,7 +2753,7 @@
       <c r="B8" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D8" s="1">
@@ -3048,7 +3030,6 @@
       <c r="A28" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="1"/>
       <c r="D28" s="1">
         <f>SUM(D3:D27)</f>
         <v>4500</v>

--- a/Assets/Document/Poker.xlsx
+++ b/Assets/Document/Poker.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game Project\Psychic-Texas-Hold-em\Assets\Document\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24210" windowHeight="14955"/>
+    <workbookView windowWidth="19200" windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="159">
   <si>
     <t>No</t>
   </si>
@@ -159,6 +164,18 @@
     <t>选择一名玩家发动，该玩家这局游戏无法弃牌</t>
   </si>
   <si>
+    <t>迟钝</t>
+  </si>
+  <si>
+    <t>选择一名玩家发动，该玩家这局游戏所有技能的发动时间x2</t>
+  </si>
+  <si>
+    <t>戏法空间</t>
+  </si>
+  <si>
+    <t>这局游戏场上所有玩家所有技能的能量消耗随机增加或降低0~2点</t>
+  </si>
+  <si>
     <t>道具名称</t>
   </si>
   <si>
@@ -246,19 +263,43 @@
     <t>神像</t>
   </si>
   <si>
-    <t>[许愿]获得的牌必定是QKA</t>
+    <t>[许愿]获得的牌必定是QKA（和魔像互斥)</t>
   </si>
   <si>
     <t>魔像</t>
   </si>
   <si>
-    <t>[许愿]获得的牌必定能凑成三条，但该局无法加注</t>
+    <t>[许愿]获得的牌必定能凑成三条，但该局无法加注（和神像互斥)</t>
   </si>
   <si>
     <t>袖章</t>
   </si>
   <si>
     <t>当玩家为场上亏损最高时，所有技能能量消耗-2（最低为1）</t>
+  </si>
+  <si>
+    <t>香薰</t>
+  </si>
+  <si>
+    <t>[迟钝]的技能效果改为x3</t>
+  </si>
+  <si>
+    <t>仙女棒</t>
+  </si>
+  <si>
+    <t>第一次使用[灵机]变化的技能时量消耗-2</t>
+  </si>
+  <si>
+    <t>可乐</t>
+  </si>
+  <si>
+    <t>[透支]的技能禁用时间减为2局</t>
+  </si>
+  <si>
+    <t>酒</t>
+  </si>
+  <si>
+    <t>每次加注恢复1点能量</t>
   </si>
   <si>
     <t>筹码</t>
@@ -642,12 +683,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -966,7 +1013,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -990,16 +1037,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1008,89 +1055,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1106,6 +1153,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1427,7 +1481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1644,11 +1698,11 @@
       <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="7">
         <v>2</v>
       </c>
-      <c r="D11" s="5">
-        <v>2</v>
+      <c r="D11" s="7">
+        <v>3</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
@@ -1818,83 +1872,73 @@
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="J20">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="7">
+        <v>2</v>
+      </c>
+      <c r="D20" s="7">
+        <v>3</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="7">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="7">
+        <v>5</v>
+      </c>
+      <c r="D21" s="7">
+        <v>4</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="J22">
         <v>6</v>
       </c>
-      <c r="K20">
+      <c r="K22">
         <v>8</v>
       </c>
-      <c r="L20">
+      <c r="L22">
         <v>10</v>
       </c>
-      <c r="M20">
+      <c r="M22">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="3" t="s">
+    <row r="23" spans="1:13">
+      <c r="A23" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="1">
-        <v>1</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="1">
-        <v>2</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>30</v>
-      </c>
-      <c r="J23">
-        <f t="shared" ref="J23:J28" si="0">I23*$J$20</f>
-        <v>180</v>
-      </c>
-      <c r="K23">
-        <f t="shared" ref="K23:K28" si="1">I23*$K$20</f>
-        <v>240</v>
-      </c>
-      <c r="L23">
-        <f t="shared" ref="L23:L28" si="2">I23*$L$20</f>
-        <v>300</v>
-      </c>
-      <c r="M23">
-        <f t="shared" ref="M23:M28" si="3">I23*$M$20</f>
-        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -1905,207 +1949,228 @@
       <c r="F24" s="1">
         <v>0</v>
       </c>
-      <c r="H24">
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="1">
         <v>2</v>
       </c>
-      <c r="I24">
+      <c r="B25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>30</v>
+      </c>
+      <c r="J25">
+        <f t="shared" ref="J25:J30" si="0">I25*$J$22</f>
+        <v>180</v>
+      </c>
+      <c r="K25">
+        <f t="shared" ref="K25:K30" si="1">I25*$K$22</f>
+        <v>240</v>
+      </c>
+      <c r="L25">
+        <f t="shared" ref="L25:L30" si="2">I25*$L$22</f>
+        <v>300</v>
+      </c>
+      <c r="M25">
+        <f t="shared" ref="M25:M30" si="3">I25*$M$22</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="1">
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
         <v>20</v>
       </c>
-      <c r="J24">
+      <c r="J26">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="K24">
+      <c r="K26">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="L24">
+      <c r="L26">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="M24">
+      <c r="M26">
         <f t="shared" si="3"/>
         <v>240</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="1">
+    <row r="27" spans="1:13">
+      <c r="A27" s="1">
         <v>4</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="B27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="1">
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="H27">
         <v>3</v>
       </c>
-      <c r="I25">
+      <c r="I27">
         <v>15</v>
       </c>
-      <c r="J25">
+      <c r="J27">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="K25">
+      <c r="K27">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="L25">
+      <c r="L27">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="M25">
+      <c r="M27">
         <f t="shared" si="3"/>
         <v>180</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="1">
+    <row r="28" spans="1:13">
+      <c r="A28" s="1">
         <v>5</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="1">
+      <c r="B28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" s="1">
         <v>400</v>
       </c>
-      <c r="H26">
+      <c r="H28">
         <v>4</v>
       </c>
-      <c r="I26">
+      <c r="I28">
         <v>10</v>
       </c>
-      <c r="J26">
+      <c r="J28">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K26">
+      <c r="K28">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="L26">
+      <c r="L28">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="M26">
+      <c r="M28">
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="1">
+    <row r="29" spans="1:13">
+      <c r="A29" s="1">
         <v>6</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="1">
+      <c r="B29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="1">
         <v>400</v>
       </c>
-      <c r="H27">
+      <c r="H29">
         <v>5</v>
       </c>
-      <c r="I27">
+      <c r="I29">
         <v>5</v>
       </c>
-      <c r="J27">
+      <c r="J29">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="K27">
+      <c r="K29">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L27">
+      <c r="L29">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="M27">
+      <c r="M29">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="1">
+    <row r="30" spans="1:13">
+      <c r="A30" s="1">
         <v>7</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F28" s="1">
+      <c r="B30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="1">
         <v>400</v>
       </c>
-      <c r="H28">
+      <c r="H30">
         <v>6</v>
       </c>
-      <c r="I28">
+      <c r="I30">
         <v>0</v>
       </c>
-      <c r="J28">
+      <c r="J30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K28">
+      <c r="K30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28">
+      <c r="L30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M28">
+      <c r="M30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="1">
-        <v>8</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="1">
-        <v>400</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="1">
-        <v>9</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="1">
-        <v>400</v>
-      </c>
-    </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>10</v>
-      </c>
-      <c r="B31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2114,12 +2179,13 @@
       <c r="F31" s="1">
         <v>400</v>
       </c>
+      <c r="H31" s="1"/>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>11</v>
-      </c>
-      <c r="B32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2131,9 +2197,9 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1">
-        <v>12</v>
-      </c>
-      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2145,12 +2211,12 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1">
-        <v>13</v>
-      </c>
-      <c r="B34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F34" s="1">
@@ -2159,7 +2225,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>71</v>
@@ -2173,12 +2239,12 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="6" t="s">
         <v>74</v>
       </c>
       <c r="F36" s="1">
@@ -2187,7 +2253,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>75</v>
@@ -2199,446 +2265,541 @@
         <v>400</v>
       </c>
     </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1">
+        <v>15</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="1">
+        <v>400</v>
+      </c>
+    </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="1">
+        <v>16</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="7">
+        <v>17</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="7">
+        <v>18</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="7">
+        <v>19</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="7">
+        <v>20</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="C44" s="2"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="1">
+      <c r="B46" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1">
         <v>1</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B47" s="1">
         <v>3000</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C47" s="1">
         <v>30</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D47" s="1">
         <v>30</v>
       </c>
-      <c r="E40" s="1">
-        <f t="shared" ref="E40:E47" si="4">D40/C40</f>
+      <c r="E47" s="1">
+        <f t="shared" ref="E47:E54" si="4">D47/C47</f>
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="1">
+    <row r="48" spans="1:6">
+      <c r="A48" s="1">
         <v>2</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B48" s="1">
         <v>6000</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C48" s="1">
         <v>60</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D48" s="1">
         <v>55</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E48" s="1">
         <f t="shared" si="4"/>
         <v>0.916666666666667</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1">
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
         <v>3</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B49" s="1">
         <v>10000</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C49" s="1">
         <v>100</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D49" s="1">
         <v>90</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E49" s="1">
         <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="1">
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
         <v>4</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B50" s="1">
         <v>30000</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C50" s="1">
         <v>300</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D50" s="1">
         <v>260</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E50" s="1">
         <f t="shared" si="4"/>
         <v>0.866666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="1">
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
         <v>5</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B51" s="1">
         <v>50000</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C51" s="1">
         <v>500</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D51" s="1">
         <v>420</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E51" s="1">
         <f t="shared" si="4"/>
         <v>0.84</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="1">
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
         <v>6</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B52" s="1">
         <v>100000</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C52" s="1">
         <v>1000</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D52" s="1">
         <v>800</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E52" s="1">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="1">
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
         <v>7</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B53" s="1">
         <v>300000</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C53" s="1">
         <v>3000</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D53" s="1">
         <v>2300</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E53" s="1">
         <f t="shared" si="4"/>
         <v>0.766666666666667</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="1">
+    <row r="54" spans="1:5">
+      <c r="A54" s="1">
         <v>8</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B54" s="1">
         <v>500000</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C54" s="1">
         <v>5000</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D54" s="1">
         <v>3600</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E54" s="1">
         <f t="shared" si="4"/>
         <v>0.72</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="3" t="s">
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="1">
+      <c r="B56" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" s="3"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1">
         <v>1</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B57" s="1">
         <v>300</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C57" s="1">
         <v>1</v>
       </c>
-      <c r="E50" s="1">
-        <f t="shared" ref="E50:E57" si="5">B50/C50</f>
+      <c r="E57" s="1">
+        <f t="shared" ref="E57:E64" si="5">B57/C57</f>
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="1">
+    <row r="58" spans="1:5">
+      <c r="A58" s="1">
         <v>2</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B58" s="1">
         <v>630</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C58" s="1">
         <v>2</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E58" s="1">
         <f t="shared" si="5"/>
         <v>315</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="1">
+    <row r="59" spans="1:5">
+      <c r="A59" s="1">
         <v>3</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B59" s="1">
         <v>1650</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C59" s="1">
         <v>5</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E59" s="1">
         <f t="shared" si="5"/>
         <v>330</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="1">
+    <row r="60" spans="1:5">
+      <c r="A60" s="1">
         <v>4</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B60" s="1">
         <v>3500</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C60" s="1">
         <v>10</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E60" s="1">
         <f t="shared" si="5"/>
         <v>350</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="1">
+    <row r="61" spans="1:5">
+      <c r="A61" s="1">
         <v>5</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B61" s="1">
         <v>5600</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C61" s="1">
         <v>15</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E61" s="1">
         <f t="shared" si="5"/>
         <v>373.333333333333</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="1">
+    <row r="62" spans="1:5">
+      <c r="A62" s="1">
         <v>6</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B62" s="1">
         <v>8000</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C62" s="1">
         <v>20</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E62" s="1">
         <f t="shared" si="5"/>
         <v>400</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="1">
+    <row r="63" spans="1:5">
+      <c r="A63" s="1">
         <v>7</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B63" s="1">
         <v>12600</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C63" s="1">
         <v>30</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E63" s="1">
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="1">
+    <row r="64" spans="1:5">
+      <c r="A64" s="1">
         <v>8</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B64" s="1">
         <v>22000</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C64" s="1">
         <v>50</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E64" s="1">
         <f t="shared" si="5"/>
         <v>440</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="3" t="s">
+    <row r="66" spans="1:8">
+      <c r="A66" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="1">
+      <c r="B66" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1">
         <v>1</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="B67" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" s="1">
         <v>4.99</v>
       </c>
-      <c r="H60">
+      <c r="H67">
         <v>8100</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="1">
+    <row r="68" spans="1:8">
+      <c r="A68" s="1">
         <v>2</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D61" s="1">
+      <c r="B68" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" s="1">
         <v>1.99</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="3" t="s">
+    <row r="70" spans="1:8">
+      <c r="A70" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="1">
+      <c r="B70" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1">
         <v>1</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B71" t="s">
         <v>13</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E64" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="1">
+      <c r="C71" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1">
         <v>2</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B72" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E65" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="1">
+      <c r="C72" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1">
         <v>3</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B73" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E66" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="1">
+      <c r="C73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1">
         <v>4</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B74" t="s">
         <v>35</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E67" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="1">
+      <c r="C74" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1">
         <v>5</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B75" t="s">
         <v>35</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E68" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="1">
+      <c r="C75" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1">
         <v>6</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B76" t="s">
         <v>39</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E69" t="s">
-        <v>57</v>
+      <c r="C76" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E76" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2667,13 +2828,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2681,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D3" s="1">
         <v>20</v>
@@ -2695,10 +2856,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D4" s="1">
         <v>30</v>
@@ -2709,10 +2870,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D5" s="1">
         <v>50</v>
@@ -2723,10 +2884,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -2737,10 +2898,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D7" s="1">
         <v>300</v>
@@ -2751,10 +2912,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D8" s="1">
         <v>500</v>
@@ -2765,10 +2926,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D9" s="1">
         <v>20</v>
@@ -2779,10 +2940,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D10" s="1">
         <v>30</v>
@@ -2793,10 +2954,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D11" s="1">
         <v>50</v>
@@ -2807,10 +2968,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
@@ -2821,10 +2982,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D13" s="1">
         <v>300</v>
@@ -2835,10 +2996,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D14" s="1">
         <v>500</v>
@@ -2849,10 +3010,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D15" s="1">
         <v>20</v>
@@ -2863,10 +3024,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D16" s="1">
         <v>30</v>
@@ -2877,10 +3038,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D17" s="1">
         <v>50</v>
@@ -2891,10 +3052,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
@@ -2905,10 +3066,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D19" s="1">
         <v>300</v>
@@ -2919,10 +3080,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D20" s="1">
         <v>500</v>
@@ -2933,10 +3094,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
@@ -2947,10 +3108,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>
@@ -2961,10 +3122,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
@@ -2975,10 +3136,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D24" s="1">
         <v>200</v>
@@ -2989,10 +3150,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D25" s="1">
         <v>200</v>
@@ -3003,10 +3164,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D26" s="1">
         <v>300</v>
@@ -3017,10 +3178,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="D27" s="1">
         <v>500</v>
@@ -3028,7 +3189,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D28" s="1">
         <f>SUM(D3:D27)</f>

--- a/Assets/Document/Poker.xlsx
+++ b/Assets/Document/Poker.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="213">
   <si>
     <t>No</t>
   </si>
@@ -41,6 +41,9 @@
     <t>技能名称</t>
   </si>
   <si>
+    <t>技能名称EN</t>
+  </si>
+  <si>
     <t>能量消耗</t>
   </si>
   <si>
@@ -50,12 +53,24 @@
     <t>技能效果</t>
   </si>
   <si>
+    <t>参数1</t>
+  </si>
+  <si>
+    <t>参数数值</t>
+  </si>
+  <si>
+    <t>参数2</t>
+  </si>
+  <si>
     <t>价格</t>
   </si>
   <si>
     <t>抵抗</t>
   </si>
   <si>
+    <t>Resist</t>
+  </si>
+  <si>
     <t>X</t>
   </si>
   <si>
@@ -65,117 +80,192 @@
     <t>感应</t>
   </si>
   <si>
+    <t>Sense</t>
+  </si>
+  <si>
     <t>发动后这局游戏可以查看其他玩家的能量，且当其他玩家发动技能时进行提示</t>
   </si>
   <si>
     <t>透视</t>
   </si>
   <si>
+    <t>Peek</t>
+  </si>
+  <si>
     <t>选择一张对手底牌或公牌发动，这张牌显示3秒</t>
   </si>
   <si>
+    <t>显示时间</t>
+  </si>
+  <si>
     <t>变牌</t>
   </si>
   <si>
+    <t>Change</t>
+  </si>
+  <si>
     <t>选择场上玩家一张底牌发动，将这张牌替换为剩余牌库中的某张牌</t>
   </si>
   <si>
     <t>模糊</t>
   </si>
   <si>
+    <t>Blur</t>
+  </si>
+  <si>
     <t>选择一名玩家发动，该玩家这局游戏无法看清手牌和公牌</t>
   </si>
   <si>
     <t>干扰</t>
   </si>
   <si>
+    <t>Interfere</t>
+  </si>
+  <si>
     <t>选择一名玩家发动，该玩家这局游戏发动技能有35%概率失败，可叠加</t>
   </si>
   <si>
+    <t>失败概率</t>
+  </si>
+  <si>
     <t>颠倒</t>
   </si>
   <si>
+    <t>Upsidedown</t>
+  </si>
+  <si>
     <t>选择一名玩家发动，该玩家这局游戏画面颠倒</t>
   </si>
   <si>
+    <t>迟钝</t>
+  </si>
+  <si>
+    <t>Slow</t>
+  </si>
+  <si>
+    <t>选择一名玩家发动，该玩家这局游戏所有技能的发动时间x2</t>
+  </si>
+  <si>
+    <t>发动时间倍率</t>
+  </si>
+  <si>
     <t>枷锁</t>
   </si>
   <si>
+    <t>Chain</t>
+  </si>
+  <si>
     <t>选择一名玩家发动，该玩家这局游戏只能再使用3次技能</t>
   </si>
   <si>
+    <t>使用次数限制</t>
+  </si>
+  <si>
     <t>共鸣</t>
   </si>
   <si>
+    <t>Resonance</t>
+  </si>
+  <si>
     <t>如果场上其他玩家有和你同类的牌型，这些牌会进行闪烁</t>
   </si>
   <si>
     <t>援助</t>
   </si>
   <si>
+    <t>Help</t>
+  </si>
+  <si>
     <t>选择一名玩家发动，恢复其3点能量</t>
   </si>
   <si>
+    <t>能量恢复</t>
+  </si>
+  <si>
     <t>封印</t>
   </si>
   <si>
+    <t>Seal</t>
+  </si>
+  <si>
     <t>选择场上玩家一张底牌发动，这张牌被遮挡，且免疫[透视]、[变牌]、[交换]</t>
   </si>
   <si>
     <t>灵机</t>
   </si>
   <si>
+    <t>Idea</t>
+  </si>
+  <si>
     <t>发动后这局游戏该技能会随机变成其他任意技能</t>
   </si>
   <si>
     <t>透支</t>
   </si>
   <si>
+    <t>Overdraw</t>
+  </si>
+  <si>
     <t>能量恢复至最大，但接下来三局无法使用任何技能</t>
   </si>
   <si>
+    <t>技能禁用时间</t>
+  </si>
+  <si>
     <t>交换</t>
   </si>
   <si>
+    <t>Swap</t>
+  </si>
+  <si>
     <t>选择场上任意2张牌发动，将这2张牌进行调换</t>
   </si>
   <si>
     <t>许愿</t>
   </si>
   <si>
+    <t>Wish</t>
+  </si>
+  <si>
     <t>发动后下一局游戏的2张底牌必定是JQKA</t>
   </si>
   <si>
     <t>重力场</t>
   </si>
   <si>
+    <t>Gravity</t>
+  </si>
+  <si>
     <t>这局游戏场上能量最高的玩家所有技能能量消耗+2</t>
   </si>
   <si>
+    <t>戏法空间</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>这局游戏场上所有玩家所有技能的能量消耗随机增加或降低0~2点</t>
+  </si>
+  <si>
     <t>反射壁</t>
   </si>
   <si>
+    <t>Reflect</t>
+  </si>
+  <si>
     <t>发动后这局游戏受到其他玩家的技能时，技能会被反弹给其他任意一名玩家</t>
   </si>
   <si>
     <t>精神控制</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>选择一名玩家发动，该玩家这局游戏无法弃牌</t>
   </si>
   <si>
-    <t>迟钝</t>
-  </si>
-  <si>
-    <t>选择一名玩家发动，该玩家这局游戏所有技能的发动时间x2</t>
-  </si>
-  <si>
-    <t>戏法空间</t>
-  </si>
-  <si>
-    <t>这局游戏场上所有玩家所有技能的能量消耗随机增加或降低0~2点</t>
-  </si>
-  <si>
     <t>道具名称</t>
   </si>
   <si>
@@ -185,121 +275,193 @@
     <t>项链</t>
   </si>
   <si>
+    <t>Necklace</t>
+  </si>
+  <si>
     <t>能量上限+5</t>
   </si>
   <si>
+    <t>能量上限</t>
+  </si>
+  <si>
     <t>烟斗</t>
   </si>
   <si>
+    <t>Pipe</t>
+  </si>
+  <si>
     <t>能量恢复+1</t>
   </si>
   <si>
     <t>奖牌</t>
   </si>
   <si>
+    <t>Medal</t>
+  </si>
+  <si>
     <t>能量恢复-1，获胜则下轮游戏能量上限+3，并恢复全部能量</t>
   </si>
   <si>
     <t>怀表</t>
   </si>
   <si>
+    <t>Watch</t>
+  </si>
+  <si>
     <t>所有技能发动时间-70%</t>
   </si>
   <si>
+    <t>发动时间</t>
+  </si>
+  <si>
+    <t>啤酒</t>
+  </si>
+  <si>
+    <t>Beer</t>
+  </si>
+  <si>
+    <t>每次加注恢复1点能量</t>
+  </si>
+  <si>
     <t>磁线圈</t>
   </si>
   <si>
+    <t>Coil</t>
+  </si>
+  <si>
     <t>能量上限-6，能量恢复-2，每当其他玩家成功发动技能，恢复1点能量</t>
   </si>
   <si>
     <t>兽爪</t>
   </si>
   <si>
+    <t>Claw</t>
+  </si>
+  <si>
     <t>如果只选择了2个技能，对方抵抗这两个技能需要额外消耗1点能量</t>
   </si>
   <si>
+    <t>抵抗能量消耗</t>
+  </si>
+  <si>
     <t>斗篷</t>
   </si>
   <si>
+    <t>Cloak</t>
+  </si>
+  <si>
     <t>[抵抗]能量消耗-1</t>
   </si>
   <si>
     <t>天线</t>
   </si>
   <si>
+    <t>Antenna</t>
+  </si>
+  <si>
     <t>[感应]不消耗能量且显示玩家饰品</t>
   </si>
   <si>
     <t>帽子</t>
   </si>
   <si>
+    <t>Hat</t>
+  </si>
+  <si>
     <t>发动技能时不会被[感应]效果感知</t>
   </si>
   <si>
     <t>镜片</t>
   </si>
   <si>
+    <t>Glass</t>
+  </si>
+  <si>
     <t>[透视]将会额外随机显示场上一张牌</t>
   </si>
   <si>
     <t>眼药</t>
   </si>
   <si>
+    <t>Eyedrop</t>
+  </si>
+  <si>
     <t>[透视]显示时间提升至60秒</t>
   </si>
   <si>
     <t>戒指</t>
   </si>
   <si>
+    <t>Ring</t>
+  </si>
+  <si>
     <t>[变牌]和[交换]可以对公牌使用</t>
   </si>
   <si>
     <t>音叉</t>
   </si>
   <si>
+    <t>Fork</t>
+  </si>
+  <si>
     <t>[干扰]的技能效果+25%</t>
   </si>
   <si>
+    <t>失败概率提升</t>
+  </si>
+  <si>
+    <t>香薰</t>
+  </si>
+  <si>
+    <t>Aroma</t>
+  </si>
+  <si>
+    <t>[迟钝]的技能效果改为x3</t>
+  </si>
+  <si>
+    <t>仙女棒</t>
+  </si>
+  <si>
+    <t>Wand</t>
+  </si>
+  <si>
+    <t>第一次使用[灵机]变化的技能时量消耗-2</t>
+  </si>
+  <si>
+    <t>可乐</t>
+  </si>
+  <si>
+    <t>Cola</t>
+  </si>
+  <si>
+    <t>[透支]的技能禁用时间减为2局</t>
+  </si>
+  <si>
     <t>神像</t>
   </si>
   <si>
+    <t>Statue</t>
+  </si>
+  <si>
     <t>[许愿]获得的牌必定是QKA（和魔像互斥)</t>
   </si>
   <si>
     <t>魔像</t>
   </si>
   <si>
+    <t>Golem</t>
+  </si>
+  <si>
     <t>[许愿]获得的牌必定能凑成三条，但该局无法加注（和神像互斥)</t>
   </si>
   <si>
     <t>袖章</t>
   </si>
   <si>
+    <t>Armband</t>
+  </si>
+  <si>
     <t>当玩家为场上亏损最高时，所有技能能量消耗-2（最低为1）</t>
-  </si>
-  <si>
-    <t>香薰</t>
-  </si>
-  <si>
-    <t>[迟钝]的技能效果改为x3</t>
-  </si>
-  <si>
-    <t>仙女棒</t>
-  </si>
-  <si>
-    <t>第一次使用[灵机]变化的技能时量消耗-2</t>
-  </si>
-  <si>
-    <t>可乐</t>
-  </si>
-  <si>
-    <t>[透支]的技能禁用时间减为2局</t>
-  </si>
-  <si>
-    <t>酒</t>
-  </si>
-  <si>
-    <t>每次加注恢复1点能量</t>
   </si>
   <si>
     <t>筹码</t>
@@ -1137,7 +1299,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1148,16 +1310,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1481,24 +1647,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9.475" style="1" customWidth="1"/>
-    <col min="5" max="5" width="65.8583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="3" max="3" width="11.5333333333333" style="4" customWidth="1"/>
+    <col min="4" max="5" width="9.475" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2.3" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="13.3583333333333" customWidth="1"/>
+    <col min="10" max="11" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -1510,1296 +1680,1587 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:11">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:11">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3</v>
+      </c>
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:11">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:11">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="7">
         <v>2</v>
       </c>
-      <c r="D8" s="5">
+      <c r="E8" s="7">
         <v>2</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="F8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:11">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="10">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10">
         <v>3</v>
       </c>
-      <c r="D9" s="5">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="F9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="K9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:11">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="B10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="7">
         <v>3</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" s="7">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="1">
+        <v>3</v>
+      </c>
+      <c r="K10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:11">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2</v>
+      <c r="B11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="D11" s="7">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7">
         <v>3</v>
       </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2</v>
+      </c>
+      <c r="E12" s="10">
         <v>3</v>
       </c>
-      <c r="D12" s="5">
-        <v>4</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3</v>
+      </c>
+      <c r="K12" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:11">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="1">
+      <c r="B13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="7">
+        <v>3</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:11">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="7">
         <v>0</v>
       </c>
-      <c r="D14" s="5">
-        <v>3</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="E14" s="7">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K14" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="5">
-        <v>4</v>
-      </c>
-      <c r="D15" s="5">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="B15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="1">
+        <v>3</v>
+      </c>
+      <c r="K15" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:11">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="1">
+        <v>59</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="7">
         <v>4</v>
       </c>
-      <c r="D16" s="1">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="E16" s="7">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:20">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="5">
-        <v>5</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="B17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1">
         <v>4</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="E17" s="1">
+        <v>4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:20">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="5">
-        <v>7</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="B18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="7">
         <v>5</v>
       </c>
-      <c r="E18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="1">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="E18" s="7">
+        <v>4</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
+      <c r="K18" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="5">
+      <c r="B19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="10">
+        <v>5</v>
+      </c>
+      <c r="E19" s="10">
+        <v>4</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="7">
+        <v>7</v>
+      </c>
+      <c r="E20" s="7">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>73</v>
+      </c>
+      <c r="K20" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="7">
         <v>9</v>
       </c>
-      <c r="D19" s="5">
+      <c r="E21" s="7">
         <v>7</v>
       </c>
-      <c r="E19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="F21" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="7">
+    <row r="24" spans="1:20">
+      <c r="Q24">
+        <v>6</v>
+      </c>
+      <c r="R24">
+        <v>8</v>
+      </c>
+      <c r="S24">
+        <v>10</v>
+      </c>
+      <c r="T24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" s="1">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" s="1">
+        <v>5</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" s="1">
+        <v>2</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>30</v>
+      </c>
+      <c r="Q27">
+        <f>P27*$Q$24</f>
+        <v>180</v>
+      </c>
+      <c r="R27">
+        <f>P27*$R$24</f>
+        <v>240</v>
+      </c>
+      <c r="S27">
+        <f>P27*$S$24</f>
+        <v>300</v>
+      </c>
+      <c r="T27">
+        <f>P27*$T$24</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="A28" s="1">
+        <v>3</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H28" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28" s="1">
+        <v>3</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28">
+        <v>20</v>
+      </c>
+      <c r="Q28">
+        <f>P28*$Q$24</f>
+        <v>120</v>
+      </c>
+      <c r="R28">
+        <f>P28*$R$24</f>
+        <v>160</v>
+      </c>
+      <c r="S28">
+        <f>P28*$S$24</f>
+        <v>200</v>
+      </c>
+      <c r="T28">
+        <f>P28*$T$24</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29" s="1">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="1">
+        <v>-0.7</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
+      <c r="P29">
+        <v>15</v>
+      </c>
+      <c r="Q29">
+        <f>P29*$Q$24</f>
+        <v>90</v>
+      </c>
+      <c r="R29">
+        <f>P29*$R$24</f>
+        <v>120</v>
+      </c>
+      <c r="S29">
+        <f>P29*$S$24</f>
+        <v>150</v>
+      </c>
+      <c r="T29">
+        <f>P29*$T$24</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" s="1">
+        <v>5</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31" s="1">
+        <v>6</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" s="1">
+        <v>-6</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" s="1">
+        <v>-2</v>
+      </c>
+      <c r="K31" s="1">
+        <v>400</v>
+      </c>
+      <c r="O31">
+        <v>4</v>
+      </c>
+      <c r="P31">
+        <v>10</v>
+      </c>
+      <c r="Q31">
+        <f>P31*$Q$24</f>
+        <v>60</v>
+      </c>
+      <c r="R31">
+        <f>P31*$R$24</f>
+        <v>80</v>
+      </c>
+      <c r="S31">
+        <f>P31*$S$24</f>
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <f>P31*$T$24</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="A32" s="1">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>400</v>
+      </c>
+      <c r="O32">
+        <v>5</v>
+      </c>
+      <c r="P32">
+        <v>5</v>
+      </c>
+      <c r="Q32">
+        <f>P32*$Q$24</f>
+        <v>30</v>
+      </c>
+      <c r="R32">
+        <f>P32*$R$24</f>
+        <v>40</v>
+      </c>
+      <c r="S32">
+        <f>P32*$S$24</f>
+        <v>50</v>
+      </c>
+      <c r="T32">
+        <f>P32*$T$24</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33" s="1">
+        <v>8</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>400</v>
+      </c>
+      <c r="O33">
+        <v>6</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <f>P33*$Q$24</f>
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <f>P33*$R$24</f>
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <f>P33*$S$24</f>
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <f>P33*$T$24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" s="1">
+        <v>9</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K34" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35" s="1">
+        <v>10</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K35" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" s="1">
+        <v>11</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K36" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37" s="1">
+        <v>12</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="1">
+        <v>60</v>
+      </c>
+      <c r="K37" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
+      <c r="A38" s="1">
+        <v>13</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K38" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="A39" s="1">
+        <v>14</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="K39" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" s="1">
+        <v>15</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3</v>
+      </c>
+      <c r="K40" s="10">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
+      <c r="A41" s="1">
+        <v>16</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="1">
+        <v>-2</v>
+      </c>
+      <c r="K41" s="10">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="A42" s="1">
+        <v>17</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2</v>
+      </c>
+      <c r="K42" s="10">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" s="1">
+        <v>18</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K43" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="A44" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="7">
+      <c r="B44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K44" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="A45" s="1">
+        <v>20</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="1">
+        <v>-2</v>
+      </c>
+      <c r="K45" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="D50" s="2"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1">
+        <v>1</v>
+      </c>
+      <c r="B53" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D53" s="1">
+        <v>30</v>
+      </c>
+      <c r="E53" s="1">
+        <v>30</v>
+      </c>
+      <c r="F53" s="1">
+        <f t="shared" ref="F53:F60" si="0">E53/D53</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1">
         <v>2</v>
       </c>
-      <c r="D20" s="7">
+      <c r="B54" s="1">
+        <v>6000</v>
+      </c>
+      <c r="D54" s="1">
+        <v>60</v>
+      </c>
+      <c r="E54" s="1">
+        <v>55</v>
+      </c>
+      <c r="F54" s="1">
+        <f t="shared" si="0"/>
+        <v>0.916666666666667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1">
         <v>3</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="B55" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D55" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="7">
-        <v>20</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="7">
+      <c r="E55" s="1">
+        <v>90</v>
+      </c>
+      <c r="F55" s="1">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1">
+        <v>4</v>
+      </c>
+      <c r="B56" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D56" s="1">
+        <v>300</v>
+      </c>
+      <c r="E56" s="1">
+        <v>260</v>
+      </c>
+      <c r="F56" s="1">
+        <f t="shared" si="0"/>
+        <v>0.866666666666667</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="1">
         <v>5</v>
       </c>
-      <c r="D21" s="7">
+      <c r="B57" s="1">
+        <v>50000</v>
+      </c>
+      <c r="D57" s="1">
+        <v>500</v>
+      </c>
+      <c r="E57" s="1">
+        <v>420</v>
+      </c>
+      <c r="F57" s="1">
+        <f t="shared" si="0"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="1">
+        <v>6</v>
+      </c>
+      <c r="B58" s="1">
+        <v>100000</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="1">
+        <v>800</v>
+      </c>
+      <c r="F58" s="1">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="1">
+        <v>7</v>
+      </c>
+      <c r="B59" s="1">
+        <v>300000</v>
+      </c>
+      <c r="D59" s="1">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="1">
+        <v>2300</v>
+      </c>
+      <c r="F59" s="1">
+        <f t="shared" si="0"/>
+        <v>0.766666666666667</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="1">
+        <v>8</v>
+      </c>
+      <c r="B60" s="1">
+        <v>500000</v>
+      </c>
+      <c r="D60" s="1">
+        <v>5000</v>
+      </c>
+      <c r="E60" s="1">
+        <v>3600</v>
+      </c>
+      <c r="F60" s="1">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="1">
+        <v>1</v>
+      </c>
+      <c r="B63" s="1">
+        <v>300</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
+        <f t="shared" ref="F63:F70" si="1">B63/D63</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="1">
+        <v>2</v>
+      </c>
+      <c r="B64" s="1">
+        <v>630</v>
+      </c>
+      <c r="D64" s="1">
+        <v>2</v>
+      </c>
+      <c r="F64" s="1">
+        <f t="shared" si="1"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1">
+        <v>3</v>
+      </c>
+      <c r="B65" s="1">
+        <v>1650</v>
+      </c>
+      <c r="D65" s="1">
+        <v>5</v>
+      </c>
+      <c r="F65" s="1">
+        <f t="shared" si="1"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1">
         <v>4</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="J22">
-        <v>6</v>
-      </c>
-      <c r="K22">
-        <v>8</v>
-      </c>
-      <c r="L22">
+      <c r="B66" s="1">
+        <v>3500</v>
+      </c>
+      <c r="D66" s="1">
         <v>10</v>
       </c>
-      <c r="M22">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="1">
-        <v>1</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="1">
-        <v>2</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>30</v>
-      </c>
-      <c r="J25">
-        <f t="shared" ref="J25:J30" si="0">I25*$J$22</f>
-        <v>180</v>
-      </c>
-      <c r="K25">
-        <f t="shared" ref="K25:K30" si="1">I25*$K$22</f>
-        <v>240</v>
-      </c>
-      <c r="L25">
-        <f t="shared" ref="L25:L30" si="2">I25*$L$22</f>
-        <v>300</v>
-      </c>
-      <c r="M25">
-        <f t="shared" ref="M25:M30" si="3">I25*$M$22</f>
-        <v>360</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="1">
-        <v>3</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>2</v>
-      </c>
-      <c r="I26">
-        <v>20</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="0"/>
-        <v>120</v>
-      </c>
-      <c r="K26">
+      <c r="F66" s="1">
         <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="L26">
-        <f t="shared" si="2"/>
-        <v>200</v>
-      </c>
-      <c r="M26">
-        <f t="shared" si="3"/>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="1">
-        <v>4</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-      <c r="I27">
-        <v>15</v>
-      </c>
-      <c r="J27">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="L27">
-        <f t="shared" si="2"/>
-        <v>150</v>
-      </c>
-      <c r="M27">
-        <f t="shared" si="3"/>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="1">
-        <v>5</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F28" s="1">
-        <v>400</v>
-      </c>
-      <c r="H28">
-        <v>4</v>
-      </c>
-      <c r="I28">
-        <v>10</v>
-      </c>
-      <c r="J28">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="L28">
-        <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="M28">
-        <f t="shared" si="3"/>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="1">
-        <v>6</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="1">
-        <v>400</v>
-      </c>
-      <c r="H29">
-        <v>5</v>
-      </c>
-      <c r="I29">
-        <v>5</v>
-      </c>
-      <c r="J29">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="L29">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="M29">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="1">
-        <v>7</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="1">
-        <v>400</v>
-      </c>
-      <c r="H30">
-        <v>6</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="1">
-        <v>8</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="1">
-        <v>400</v>
-      </c>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="1">
-        <v>9</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F32" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="1">
-        <v>10</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F33" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="1">
-        <v>11</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F34" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="1">
-        <v>12</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F35" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1">
-        <v>13</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F36" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1">
-        <v>14</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F37" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1">
-        <v>15</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F38" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1">
-        <v>16</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F39" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="7">
-        <v>17</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="7">
-        <v>18</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="7">
-        <v>19</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="7">
-        <v>20</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="C44" s="2"/>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="1">
-        <v>1</v>
-      </c>
-      <c r="B47" s="1">
-        <v>3000</v>
-      </c>
-      <c r="C47" s="1">
-        <v>30</v>
-      </c>
-      <c r="D47" s="1">
-        <v>30</v>
-      </c>
-      <c r="E47" s="1">
-        <f t="shared" ref="E47:E54" si="4">D47/C47</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="1">
-        <v>2</v>
-      </c>
-      <c r="B48" s="1">
-        <v>6000</v>
-      </c>
-      <c r="C48" s="1">
-        <v>60</v>
-      </c>
-      <c r="D48" s="1">
-        <v>55</v>
-      </c>
-      <c r="E48" s="1">
-        <f t="shared" si="4"/>
-        <v>0.916666666666667</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="1">
-        <v>3</v>
-      </c>
-      <c r="B49" s="1">
-        <v>10000</v>
-      </c>
-      <c r="C49" s="1">
-        <v>100</v>
-      </c>
-      <c r="D49" s="1">
-        <v>90</v>
-      </c>
-      <c r="E49" s="1">
-        <f t="shared" si="4"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="1">
-        <v>4</v>
-      </c>
-      <c r="B50" s="1">
-        <v>30000</v>
-      </c>
-      <c r="C50" s="1">
-        <v>300</v>
-      </c>
-      <c r="D50" s="1">
-        <v>260</v>
-      </c>
-      <c r="E50" s="1">
-        <f t="shared" si="4"/>
-        <v>0.866666666666667</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="1">
-        <v>5</v>
-      </c>
-      <c r="B51" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C51" s="1">
-        <v>500</v>
-      </c>
-      <c r="D51" s="1">
-        <v>420</v>
-      </c>
-      <c r="E51" s="1">
-        <f t="shared" si="4"/>
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="1">
-        <v>6</v>
-      </c>
-      <c r="B52" s="1">
-        <v>100000</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D52" s="1">
-        <v>800</v>
-      </c>
-      <c r="E52" s="1">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="1">
-        <v>7</v>
-      </c>
-      <c r="B53" s="1">
-        <v>300000</v>
-      </c>
-      <c r="C53" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D53" s="1">
-        <v>2300</v>
-      </c>
-      <c r="E53" s="1">
-        <f t="shared" si="4"/>
-        <v>0.766666666666667</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="1">
-        <v>8</v>
-      </c>
-      <c r="B54" s="1">
-        <v>500000</v>
-      </c>
-      <c r="C54" s="1">
-        <v>5000</v>
-      </c>
-      <c r="D54" s="1">
-        <v>3600</v>
-      </c>
-      <c r="E54" s="1">
-        <f t="shared" si="4"/>
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" s="3"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="1">
-        <v>1</v>
-      </c>
-      <c r="B57" s="1">
-        <v>300</v>
-      </c>
-      <c r="C57" s="1">
-        <v>1</v>
-      </c>
-      <c r="E57" s="1">
-        <f t="shared" ref="E57:E64" si="5">B57/C57</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="1">
-        <v>2</v>
-      </c>
-      <c r="B58" s="1">
-        <v>630</v>
-      </c>
-      <c r="C58" s="1">
-        <v>2</v>
-      </c>
-      <c r="E58" s="1">
-        <f t="shared" si="5"/>
-        <v>315</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="1">
-        <v>3</v>
-      </c>
-      <c r="B59" s="1">
-        <v>1650</v>
-      </c>
-      <c r="C59" s="1">
-        <v>5</v>
-      </c>
-      <c r="E59" s="1">
-        <f t="shared" si="5"/>
-        <v>330</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="1">
-        <v>4</v>
-      </c>
-      <c r="B60" s="1">
-        <v>3500</v>
-      </c>
-      <c r="C60" s="1">
-        <v>10</v>
-      </c>
-      <c r="E60" s="1">
-        <f t="shared" si="5"/>
         <v>350</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="1">
-        <v>5</v>
-      </c>
-      <c r="B61" s="1">
-        <v>5600</v>
-      </c>
-      <c r="C61" s="1">
-        <v>15</v>
-      </c>
-      <c r="E61" s="1">
-        <f t="shared" si="5"/>
-        <v>373.333333333333</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="1">
-        <v>6</v>
-      </c>
-      <c r="B62" s="1">
-        <v>8000</v>
-      </c>
-      <c r="C62" s="1">
-        <v>20</v>
-      </c>
-      <c r="E62" s="1">
-        <f t="shared" si="5"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="1">
-        <v>7</v>
-      </c>
-      <c r="B63" s="1">
-        <v>12600</v>
-      </c>
-      <c r="C63" s="1">
-        <v>30</v>
-      </c>
-      <c r="E63" s="1">
-        <f t="shared" si="5"/>
-        <v>420</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="1">
-        <v>8</v>
-      </c>
-      <c r="B64" s="1">
-        <v>22000</v>
-      </c>
-      <c r="C64" s="1">
-        <v>50</v>
-      </c>
-      <c r="E64" s="1">
-        <f t="shared" si="5"/>
-        <v>440</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>1</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="B67" s="1">
+        <v>5600</v>
       </c>
       <c r="D67" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="H67">
-        <v>8100</v>
+        <v>15</v>
+      </c>
+      <c r="F67" s="1">
+        <f t="shared" si="1"/>
+        <v>373.333333333333</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>2</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>95</v>
+        <v>6</v>
+      </c>
+      <c r="B68" s="1">
+        <v>8000</v>
       </c>
       <c r="D68" s="1">
-        <v>1.99</v>
+        <v>20</v>
+      </c>
+      <c r="F68" s="1">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1">
+        <v>7</v>
+      </c>
+      <c r="B69" s="1">
+        <v>12600</v>
+      </c>
+      <c r="D69" s="1">
+        <v>30</v>
+      </c>
+      <c r="F69" s="1">
+        <f t="shared" si="1"/>
+        <v>420</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="1">
+        <v>8</v>
+      </c>
+      <c r="B70" s="1">
+        <v>22000</v>
+      </c>
+      <c r="D70" s="1">
+        <v>50</v>
+      </c>
+      <c r="F70" s="1">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="1">
-        <v>1</v>
-      </c>
-      <c r="B71" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E71" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="1">
-        <v>2</v>
-      </c>
-      <c r="B72" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E72" t="s">
-        <v>55</v>
+      <c r="B72" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>3</v>
-      </c>
-      <c r="B73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E73" t="s">
-        <v>73</v>
+        <v>1</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E73" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H73" s="1">
+        <v>8100</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
+        <v>2</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="5"/>
+      <c r="D76" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1">
+        <v>1</v>
+      </c>
+      <c r="B77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1">
+        <v>2</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F78" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1">
+        <v>3</v>
+      </c>
+      <c r="B79" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F79" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1">
         <v>4</v>
       </c>
-      <c r="B74" t="s">
-        <v>35</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="B80" t="s">
+        <v>62</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="1">
+        <v>5</v>
+      </c>
+      <c r="B81" t="s">
+        <v>62</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F81" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="1">
+        <v>6</v>
+      </c>
+      <c r="B82" t="s">
+        <v>71</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F82" t="s">
         <v>103</v>
-      </c>
-      <c r="E74" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="1">
-        <v>5</v>
-      </c>
-      <c r="B75" t="s">
-        <v>35</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="1">
-        <v>6</v>
-      </c>
-      <c r="B76" t="s">
-        <v>39</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E76" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2828,13 +3289,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2842,10 +3303,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="D3" s="1">
         <v>20</v>
@@ -2856,10 +3317,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="D4" s="1">
         <v>30</v>
@@ -2870,10 +3331,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="D5" s="1">
         <v>50</v>
@@ -2884,10 +3345,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -2898,10 +3359,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="D7" s="1">
         <v>300</v>
@@ -2912,10 +3373,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="D8" s="1">
         <v>500</v>
@@ -2926,10 +3387,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="D9" s="1">
         <v>20</v>
@@ -2940,10 +3401,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="D10" s="1">
         <v>30</v>
@@ -2954,10 +3415,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="D11" s="1">
         <v>50</v>
@@ -2968,10 +3429,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
@@ -2982,10 +3443,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="D13" s="1">
         <v>300</v>
@@ -2996,10 +3457,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="D14" s="1">
         <v>500</v>
@@ -3010,10 +3471,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="D15" s="1">
         <v>20</v>
@@ -3024,10 +3485,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="D16" s="1">
         <v>30</v>
@@ -3038,10 +3499,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="D17" s="1">
         <v>50</v>
@@ -3052,10 +3513,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
@@ -3066,10 +3527,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="D19" s="1">
         <v>300</v>
@@ -3080,10 +3541,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="D20" s="1">
         <v>500</v>
@@ -3094,10 +3555,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
@@ -3108,10 +3569,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>
@@ -3122,10 +3583,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
@@ -3136,10 +3597,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="D24" s="1">
         <v>200</v>
@@ -3150,10 +3611,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="D25" s="1">
         <v>200</v>
@@ -3164,10 +3625,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="D26" s="1">
         <v>300</v>
@@ -3178,10 +3639,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="D27" s="1">
         <v>500</v>
@@ -3189,7 +3650,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="D28" s="1">
         <f>SUM(D3:D27)</f>
